--- a/data/Negociado_de_Policia/npprVDedad.xlsx
+++ b/data/Negociado_de_Policia/npprVDedad.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Negociado_de_Policia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F63B361-8FFA-4FB5-9BEC-4B93846CDAC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F124A0-FDA7-4D37-9AEF-439112183796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8340" yWindow="2304" windowWidth="12564" windowHeight="9384" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2021" sheetId="2" r:id="rId1"/>
@@ -430,9 +430,9 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="41.6640625" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" customWidth="1"/>
-    <col min="5" max="5" width="13.33203125" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -440,16 +440,16 @@
         <v>6</v>
       </c>
       <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
         <v>5</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -457,16 +457,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <f>SUM(B2:C2)</f>
         <v>11</v>
-      </c>
-      <c r="C2" s="2">
-        <v>10</v>
-      </c>
-      <c r="D2" s="2">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -474,16 +475,17 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
+        <v>2363</v>
+      </c>
+      <c r="C3" s="2">
+        <v>322</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <f>SUM(B3:C3)</f>
         <v>2685</v>
-      </c>
-      <c r="C3" s="2">
-        <v>2363</v>
-      </c>
-      <c r="D3" s="2">
-        <v>322</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -491,16 +493,17 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
+        <v>2433</v>
+      </c>
+      <c r="C4" s="2">
+        <v>489</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" ref="E3:E7" si="0">SUM(B4:C4)</f>
         <v>2922</v>
-      </c>
-      <c r="C4" s="2">
-        <v>2433</v>
-      </c>
-      <c r="D4" s="2">
-        <v>489</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -508,16 +511,17 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
+        <v>844</v>
+      </c>
+      <c r="C5" s="2">
+        <v>221</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2">
+        <f t="shared" si="0"/>
         <v>1065</v>
-      </c>
-      <c r="C5" s="2">
-        <v>844</v>
-      </c>
-      <c r="D5" s="2">
-        <v>221</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -525,16 +529,17 @@
         <v>10</v>
       </c>
       <c r="B6" s="2">
+        <v>244</v>
+      </c>
+      <c r="C6" s="2">
+        <v>69</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="0"/>
         <v>313</v>
-      </c>
-      <c r="C6" s="2">
-        <v>244</v>
-      </c>
-      <c r="D6" s="2">
-        <v>69</v>
-      </c>
-      <c r="E6" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -542,16 +547,17 @@
         <v>0</v>
       </c>
       <c r="B7" s="2">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="0"/>
         <v>35</v>
-      </c>
-      <c r="C7" s="2">
-        <v>26</v>
-      </c>
-      <c r="D7" s="2">
-        <v>9</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -603,6 +609,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="2">
+        <f>SUM(B2:C2)</f>
         <v>7</v>
       </c>
     </row>
@@ -620,6 +627,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="2">
+        <f t="shared" ref="E3:E7" si="0">SUM(B3:C3)</f>
         <v>2205</v>
       </c>
     </row>
@@ -637,6 +645,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
+        <f t="shared" si="0"/>
         <v>2362</v>
       </c>
     </row>
@@ -654,7 +663,8 @@
         <v>1</v>
       </c>
       <c r="E5" s="2">
-        <v>983</v>
+        <f t="shared" si="0"/>
+        <v>982</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -671,6 +681,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="2">
+        <f t="shared" si="0"/>
         <v>362</v>
       </c>
     </row>
@@ -688,7 +699,8 @@
         <v>9</v>
       </c>
       <c r="E7" s="2">
-        <v>61</v>
+        <f t="shared" si="0"/>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -739,6 +751,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="2">
+        <f>SUM(B2:C2)</f>
         <v>22</v>
       </c>
     </row>
@@ -756,6 +769,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="2">
+        <f t="shared" ref="E3:E7" si="0">SUM(B3:C3)</f>
         <v>2739</v>
       </c>
     </row>
@@ -773,6 +787,7 @@
         <v>0</v>
       </c>
       <c r="E4" s="2">
+        <f t="shared" si="0"/>
         <v>3226</v>
       </c>
     </row>
@@ -790,6 +805,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
+        <f t="shared" si="0"/>
         <v>1307</v>
       </c>
     </row>
@@ -807,6 +823,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="2">
+        <f t="shared" si="0"/>
         <v>391</v>
       </c>
     </row>
@@ -824,6 +841,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -875,6 +893,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="2">
+        <f>SUM(B2:C2)</f>
         <v>19</v>
       </c>
     </row>
@@ -892,6 +911,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="2">
+        <f t="shared" ref="E3:E7" si="0">SUM(B3:C3)</f>
         <v>3313</v>
       </c>
     </row>
@@ -909,7 +929,8 @@
         <v>4</v>
       </c>
       <c r="E4" s="2">
-        <v>4008</v>
+        <f t="shared" si="0"/>
+        <v>4004</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -926,6 +947,7 @@
         <v>0</v>
       </c>
       <c r="E5" s="2">
+        <f t="shared" si="0"/>
         <v>1650</v>
       </c>
     </row>
@@ -943,6 +965,7 @@
         <v>0</v>
       </c>
       <c r="E6" s="2">
+        <f t="shared" si="0"/>
         <v>529</v>
       </c>
     </row>
@@ -960,6 +983,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1011,6 +1035,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="2">
+        <f>SUM(B2:C2)</f>
         <v>18</v>
       </c>
     </row>
@@ -1028,7 +1053,8 @@
         <v>6</v>
       </c>
       <c r="E3" s="2">
-        <v>2918</v>
+        <f t="shared" ref="E3:E7" si="0">SUM(B3:C3)</f>
+        <v>2912</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1045,7 +1071,8 @@
         <v>4</v>
       </c>
       <c r="E4" s="2">
-        <v>3687</v>
+        <f t="shared" si="0"/>
+        <v>3683</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1062,7 +1089,8 @@
         <v>2</v>
       </c>
       <c r="E5" s="2">
-        <v>1494</v>
+        <f t="shared" si="0"/>
+        <v>1492</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1079,7 +1107,8 @@
         <v>1</v>
       </c>
       <c r="E6" s="2">
-        <v>477</v>
+        <f t="shared" si="0"/>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1096,6 +1125,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -1138,7 +1168,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -1147,7 +1177,8 @@
         <v>0</v>
       </c>
       <c r="E2" s="2">
-        <v>5</v>
+        <f>SUM(B2:C2)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1155,16 +1186,17 @@
         <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>667</v>
+        <v>1582</v>
       </c>
       <c r="C3" s="2">
-        <v>128</v>
+        <v>271</v>
       </c>
       <c r="D3" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E3" s="2">
-        <v>796</v>
+        <f t="shared" ref="E3:E7" si="0">SUM(B3:C3)</f>
+        <v>1853</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1172,16 +1204,17 @@
         <v>8</v>
       </c>
       <c r="B4" s="2">
-        <v>821</v>
+        <v>2037</v>
       </c>
       <c r="C4" s="2">
-        <v>198</v>
+        <v>433</v>
       </c>
       <c r="D4" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2">
-        <v>1025</v>
+        <f t="shared" si="0"/>
+        <v>2470</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1189,16 +1222,17 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>333</v>
+        <v>768</v>
       </c>
       <c r="C5" s="2">
-        <v>91</v>
+        <v>241</v>
       </c>
       <c r="D5" s="2">
         <v>3</v>
       </c>
       <c r="E5" s="2">
-        <v>427</v>
+        <f t="shared" si="0"/>
+        <v>1009</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1206,16 +1240,17 @@
         <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>80</v>
+        <v>219</v>
       </c>
       <c r="C6" s="2">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
       <c r="E6" s="2">
-        <v>132</v>
+        <f t="shared" si="0"/>
+        <v>326</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1223,16 +1258,17 @@
         <v>0</v>
       </c>
       <c r="B7" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2">
         <v>0</v>
       </c>
       <c r="E7" s="2">
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
